--- a/test_data/gurindji_jurlaka/data/metadata.xlsx
+++ b/test_data/gurindji_jurlaka/data/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abby/Dropbox/2026_GurindjiBirds/Birds/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/uqfmeaki/Dropbox/2026_GurindjiBirds/Birds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A92C923-0442-AA4E-9B51-642091FE2E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1BEE11-9BDE-164D-B3F6-15A432A2C959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="980" windowWidth="30240" windowHeight="17060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="860" windowWidth="30240" windowHeight="17060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RootDataset" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="272">
   <si>
     <t>name</t>
   </si>
@@ -230,9 +230,6 @@
     <t>Bush Stone Curlew</t>
   </si>
   <si>
-    <t>Wankaj nyila-ma jurlak-ma. Nyantu-ma yanana ngu wurinykarra-la marnana ngu, murluwu-ma wawurru-la-ma. Yalanginyi-ma waninyana na. Jurrkjurrkkarra na karru-ma-nga. Wal kuyangka na, nyamu-lu ngarturr-jawung-kulu-ma kurru-ma nyangana yijarni ngulu jurlak kayi panana, karu-ngku-ma yalungku-ma, nyamu-ma born wanku.</t>
-  </si>
-  <si>
     <t>Burhinus grallarius</t>
   </si>
   <si>
@@ -242,9 +239,6 @@
     <t>Emu</t>
   </si>
   <si>
-    <t>Nyawa yiparrartu kula-rnalu ngarnani karu-ngku-ma Wave Hill-la. "Mamurung kula-nta ngarlu! Ngaja-nyjurra kayarnana nyanuny-ju jamana-lu. Ngurnalu ngarlu ngantipa-rni jangkarni-lu-rni," kuya nguwuliny marnani.</t>
-  </si>
-  <si>
     <t>Dromaius novaehollandiae</t>
   </si>
   <si>
@@ -254,9 +248,6 @@
     <t>Australian Bustard or Bush Turkey</t>
   </si>
   <si>
-    <t>Pirlpirlji ngamanpurru ngarnana murlungku-ma jamut-tu-ma. Kula ngalu yiparrartu karu-yawung-kulu-ma, ngaja karrinyana ngirlkirri wankaj karu-ma. Kamparrijang-kulu marnani ngungantipangulu yurrkkarra na ngantipanguny na jaju nyampa ngunyarri.</t>
-  </si>
-  <si>
     <t>Ardeotis australis</t>
   </si>
   <si>
@@ -266,9 +257,6 @@
     <t>Willy Wagtail</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyamu-n-nga parru tampang nyila-ma jikirrij-ma, ngamayi-ma ngu tampang karru kuya. Kuyaji na nyawa-ma. Marnani ngulu-rla, nyawa-wu-ma jikirrij-ku-ma. Nomo parra, kuya, ngaja ngamayi ngaji ngaja-ngkulu tampang karru. </t>
-  </si>
-  <si>
     <t>Rhipidura leucophrys</t>
   </si>
   <si>
@@ -290,15 +278,9 @@
     <t>Black Kite or Chickenhawk</t>
   </si>
   <si>
-    <t>Karrkany-ju-ma ngumpit nguyina panana kurnpirlirn-pirrji. Karnti ngurla-nyanta nyanuny puya-ngarna yuwanana. Nyamu-wa nyila-ma ngumpit-ma panana karrkany-ju-ma karrinyana nyangunyangu na.</t>
-  </si>
-  <si>
     <t>Zebra finch</t>
   </si>
   <si>
-    <t>Nyamu-lu-nga wanku yirrpkarra-ma kuya-ma wal ngurnalu kurru nyangana. Maiti kaja-ngarna yu nou. Ngapuku-murlung-kula. "Warta niinii-walija nyila nyila. Ngulu yirrpkarra waninyana na niinii-ma, kurlpapkurlpap. Maiti ngawa-ngka. "Ngawa-wu nyangku-rla majka jeya, kuya-ma, "Karrap yijarni nyawa-ma. Billabong ngawa-yawung.</t>
-  </si>
-  <si>
     <t>Poephila guttata</t>
   </si>
   <si>
@@ -329,9 +311,6 @@
     <t>Magpie</t>
   </si>
   <si>
-    <t>Nyawa-ma kumurlawurta lintarr ngu marnana. Ngaja-n kurru nyangku kaputkaput jarrakap-jirri-ma. Kumurlawurta nyawa-ma marnana ngu lintarr nyampa-kurra-wayin? Maiti lintarr-waji nyawa-ma. Lintarr nguyina marnani kamparrijang-kulu kurnka-wu.</t>
-  </si>
-  <si>
     <t>Gymnorhina tibicen</t>
   </si>
   <si>
@@ -353,9 +332,6 @@
     <t>Channel-billed cuckoo or Christmas bird</t>
   </si>
   <si>
-    <t xml:space="preserve">Kurtakurtaka nganta marnana nyawa-ma Christmas time-ma, "Ah Christmas-ku na marnana nyila-ma." Kuya-rnangulu kurru nyangani kamparrijang-kulu marlurluka-lu-ma kajijirri-lu-ma. Christmas nyila-ma lintarr ngurla marnana. </t>
-  </si>
-  <si>
     <t>Scythops novaehollandiae</t>
   </si>
   <si>
@@ -365,9 +341,6 @@
     <t>Brolga</t>
   </si>
   <si>
-    <t>Kurrarntal-lu warrkap wanyjarnana yipu-ngka-ma. Yipu-wu marrunyu. Nyanuny-ku mangarri-wu kinyuwurra.</t>
-  </si>
-  <si>
     <t>Grus rubicunda</t>
   </si>
   <si>
@@ -389,9 +362,6 @@
     <t>Darter or Diver Duck</t>
   </si>
   <si>
-    <t>Pinka-ngarna-ma nyila-ma karrangkarrang-ma. Tarap waninyana na nyinypuruk kaninyjal. Ngurla nyangana yawu manana. Nyawa-ma kankulupala-yirri yanana pakara-la yawu-ma. Yawu na jaartkarra nyangana.</t>
-  </si>
-  <si>
     <t>Anhinga melanogaster</t>
   </si>
   <si>
@@ -449,9 +419,6 @@
     <t>Calyptorhynchus banksii</t>
   </si>
   <si>
-    <t>Walukpin tirrak partiki-wu-ngarnu-waji. Partiki ngu ngarnana murlungku-ma jurlak-kulu-ma. Karnti-ka-wu partiki-la-wu partartajkarra nyamu-lu-rla karrinyana ngulu ngarnana janypalk partiki na.</t>
-  </si>
-  <si>
     <t>files/images/Wintuk_TT.jpg</t>
   </si>
   <si>
@@ -791,12 +758,6 @@
     <t xml:space="preserve">This bird likes to eat whole seeds which grow in river areas. These seeds, called tamurung, are its favourite food. </t>
   </si>
   <si>
-    <t>The brolga dances during wet season. They are always happy when it is raining. Their favourite food is bush onions.</t>
-  </si>
-  <si>
-    <t>The channel-billed cuckoo sings when Christmas is near. "Ah it's singing for Christmas!" That's what the men and women used to say in the old days. This bird lets us know that Christmas is coming.</t>
-  </si>
-  <si>
     <t>When it's flood time, this bird calls out to let us know that the black berries are ripe.</t>
   </si>
   <si>
@@ -809,9 +770,6 @@
     <t>The corella calls out "Yakak yakak!" for example when people are returning from fishing. We hear it as it flies ahead of them calling out. It signals us that way. "Hey listen to the corella calling. Maybe they're coming back from fishing!"</t>
   </si>
   <si>
-    <t>When they flock together, we can hear them. They can help you if you're in the bush feeling thirsty. "Hey there's some finches there!" Where they flock together, that's where you should look for water. That's the place - look there. There will be a billabong full of water.</t>
-  </si>
-  <si>
     <t>This bird makes Aboriginal people into traditional healers. It does this by throwing a stick at someone's body. When bird hits the person with a stick, they become a traditional healer or 'clever man'.</t>
   </si>
   <si>
@@ -821,15 +779,6 @@
     <t>Your mother will die if you kill a willy wagtail. That's what they used to say about the willy-wagtail. "Don't kill it, or your mother and father might die!"</t>
   </si>
   <si>
-    <t>Grasshoppers and conkerberries are the favourite foods of the bush turkey. Pregnant women are not allowed to eat bush turkey, or the baby will born with a sore throat. That's what our grandmothers and great-grandmothers told us.</t>
-  </si>
-  <si>
-    <t>We were never allowed to eat emu as children on Wave Hill Station. "It's too dangerous for you mob to eat! If you do, it might kick you with its feet. Only us adults can eat it." That's what we were told.</t>
-  </si>
-  <si>
-    <t>This bird is dangerous. It walks along whistling in the scrub, then it falls over and convulses. When it gets up, that's when, if expectant mothers hear it, their babies will have fits when they're born.</t>
-  </si>
-  <si>
     <t>#VioletWadrill</t>
   </si>
   <si>
@@ -852,6 +801,60 @@
   </si>
   <si>
     <t>custom:photographerName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamut namata turturl-la ngulu ngarrungkap manani namata wupkarra-la, nyamu-wa jiyarni. “Wartarra wararr-jawung!” Wararr you know ngarrungkapkarra. Wararr-jawung ngurnalu ngalu. Lawara kula-n ngalu nyila-ma. Kula-ngkulu jayingku, kajikajirri-lu-ma, ngaja karrinyana ngirlkirri wankaj karu-ma. Nyila-rni karru nyamu marnana nyantu. Parrngart, ngirlkirri wankaj. Nyamu marnana, “Shhh-kaarra, nyila na. Well kuyany na ngaja karu-ma karrinyana, ngirlkirri-wu-ma, jarrakap-ku-ma. Jamut-ma im kuyany gigin karu-yawung-ku-ma, yapayapa-yawung-ku-ma. </t>
+  </si>
+  <si>
+    <t>Even if pregnant women wanted roasted turkey, they couldn’t eat it when it was cooking. “Hey that’s a nice fatty one”. Fat is the most desirable part you know. We would want to eat the fatty meat. But you couldn’t eat turkey. The old ladies wouldn’t give it to you in case the baby was born with a bad throat. Turkeys make a ‘shhh’ sound [which you can hear it when you're hunting]. It goes like this - sshh. Well that's how the baby will sound when it starts to talk. That’s what eating bush turkey when you're pregnant will do to you.</t>
+  </si>
+  <si>
+    <t>Nyila-ma jurlak-ma wintuk-ma-ngkula kurru karrinyani nyampayirla-lu ngarturr-jawung-kulu nyamu-yinangulu karru karrinyani. Jurlaka nyila na wurunykarraaji. Wankaj drangkarraaji. Karu-ma-lu-nga karru drangkarraaji yalanginyi-ma.  Nyamu-yinangulu ngamayi-lu kurru-ma nyangana. Wankaj nyila-ma jurlak-ma. Nyantu-ma yanana ngu wurunykarra-la marnana ngu, murluwu-ma wawurru-la-ma. Yalanginyi-ma waninyana na. Jurrkjurrkkarra na karru-ma-nga. Wal kuyangka na, nyamu-lu ngarturr-jawung-kulu-ma kurru-ma nyangana yikiliyikili-ngulu jurlak kayi panana, karu-ngku-ma yalungku-ma. Nyamu-nga born manku.</t>
+  </si>
+  <si>
+    <t>Bush stone curlews are dangerous for pregnant women to hear or be near. It whistles and moves like a drunk. Unborn babies will take after the bird. So women with small children and pregnant women can’t listen to curlews. That bird is no good. It goes along whistling in the scrub. Then it falls over. It might convulse then. It will get up afterwards. Well, if the expectant mothers hear it, the babies will follow its ways [and have fits] when they’re born.</t>
+  </si>
+  <si>
+    <t>Kula-n ngalu yiparrartu too, karu-yawung-kulu-ma, ngaja janga karrinyana yapakayi. Kuyarra-la-ma. “Wanyjarra-lu!” Kula-rnalu ngarnani kamparrijang-kulu jaartkarra-ma kuya. Nguyinangulu marnani kajijirri-ma ngaja-nta nganta ngumayijang-kulu-la. Ngaja-lu karrinyana wankaj karu. Kuya nguyinangulu marnani. Namata wararr-jawung nyamu jipij jiyarnani. Nyangani ngulu ngulu ngarramkapkarra manani you know jaartkarra-wu. Lawara, kula-nta ngalu. Ngurnalu ngalu ngantipa-rni marlurluka-lu, kajijirri-lu, jaartkarra-ma. Kula-nta ngalu, yarrulan-tu-ma kirri-ngku-ma, karu-kari-yawung-kulu-ma, wanyjarra-lu. Parik wanyjarra-lu. Kula-nta ngalu!”</t>
+  </si>
+  <si>
+    <t>You can’t eat emu either if you’re pregnant in case the baby gets sick. “You mob leave that [meat] alone!” So we never used to eat it in the old days. That’s what the old ladies used to tell us in case it affected the next generation. Because it might cause problems for the baby. That’s what they used to tell us. Even if it was a nice fatty emu cooking. The [pregnant women] used to see emu and want to eat it. “Sorry but you mob can’t eat it.  Only us old people can eat it. You mob can't have it. You’re pregnant so you have to leave that meat. Don’t have it. You mob shouldn’t eat it!”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jikirrij nyamu-n-nga parru tampang, ngamayi-ma ngu tampang karru kuya. Kuyaji na nyawa-ma. Marnani ngulu-rla, nyawa-wu-ma jikirrij-ku-ma. Nomo parra, kuya, ngaja ngamayi ngaji ngaja-ngkulu tampang karru. </t>
+  </si>
+  <si>
+    <t>Pinka-ngarna nyila-ma karrangkarrang-ma. Tarap waninyana na nyinypuruk kaninyjal. Ngurla nyangana yawu manana. Nyawa-ma kankulupala-yirri yanana pakara-la yawu-ma.  Yawu na jaartkarra nyangana.</t>
+  </si>
+  <si>
+    <t>Walukpin nyila-ma tirrak partiki-wu-ngarnu-waji. Partiki ngu ngarnana murlungku-ma jurlak-kulu-ma. Karnti-ka-wu partiki-la-wu partartajkarra nyamu-lu-rla karrinyana ngulu ngarnana janypalk partiki na.</t>
+  </si>
+  <si>
+    <t>Karrkany-ma - ngumpit nguyina panana kurnpirlirn-pirrji. Karnti ngurla-nyanta nyanuny puya-ngarna yuwanana. Nyamu-wa nyila-ma ngumpit-ma panana karrkany-ju-ma karrinyana nyangunyangu na.</t>
+  </si>
+  <si>
+    <t>Nyawa-ma kumurlawurta lintarr ngu marnana. Maitbi ngun kurru nyangku kaputkaput jarrakap-jirri-ma. Kumurlawurta nyawa-ma marnana ngu lintarr nyampa-kurra-wayin? Maiti lintarr-waji nyawa-ma. Lintarr nguyina marnani kamparrijang-kulu kurnka-wu.</t>
+  </si>
+  <si>
+    <t>Kurrarntal-lu-ma mangarri-ma-lu ngalu kinyuwurra. Kinyuwurra kurrijkurrij-karra ngarnana kurrarntal-lu-ma. Nyanuny-ma mangarri-ma kinyuwurra.</t>
+  </si>
+  <si>
+    <t>The brolga like to eat bush onions. They scratch around for them and eat them. Their favourite food is bush onions.</t>
+  </si>
+  <si>
+    <t>The channel-billed cuckoo sings when Christmas is near. "Ah it's singing for Christmas!" That's what the men and women used to say in the old days. This bird lets us know that Christmas is coming. That's the channel-billed cuckoo.</t>
+  </si>
+  <si>
+    <t>Kurtakurtaka nganta marnana nyawa-ma Christmas time-ma, "Ah Christmas-ku na marnana nyila-ma." Kuya-rnangulu kurru nyangani kamparrijang-kulu marlurluka-lu-ma kajijirri-lu-ma. Christmas nyila-ma lintarr ngurla marnana kuya. Nyawa-ma-lu jurlak kurtakurtaka.</t>
+  </si>
+  <si>
+    <t>Yuwayi nyawa na ngurnalu warra kangana jurlaka, niinii-walija. Nyamu-lu-nga wanku yirrpkarra-ma kuya-ma wal ngurnalu kurru nyangana. Maiti kaja-ngarna yu nou. Ngapuku-murlung-kula. "Warta niinii-walija nyila nyila. Ngulu yirrpkarra waninyana na niinii-ma, kurlpapkurlpap. Maiti ngawa-ngka. "Ngawa-wu nyangku-rla majka jeya, kuya-ma, "Karrap yijarni nyawa-ma. Billabong ngawa-yawung. Warta yijarni yijarni langka na. Langka na ngawa-yawung. Yijarni kuya ngawa nyawa," kuya. Nyangku na jurlaka-la yapayapa-la. Ngawa-ngkurra-ma nyamu-lu yanana.</t>
+  </si>
+  <si>
+    <t>Yes we watch out for this bird - finches. When they converge [on the waterhole] like this, well we hear them. Maybe when you're in the bush feeling thirsty you know. "Hey finches there and there!" They converge to the water's edge. Try looking for water there. True have a look here. A billabong with water. Hey true there's a billabong. A billabong full of water. True - there's water here. Look for the small birds when they fly to the water.</t>
+  </si>
+  <si>
+    <t>files/audio/names/tuwakin_vw.mp3</t>
   </si>
 </sst>
 </file>
@@ -920,7 +923,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -938,6 +941,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1277,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1285,7 +1291,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1366,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>13</v>
@@ -1390,7 +1396,7 @@
         <v>19</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>20</v>
@@ -1408,7 +1414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="160" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="304" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="str">
         <f t="shared" ref="A2:A21" si="0">_xlfn.CONCAT("#", C2)</f>
         <v>#wintuk</v>
@@ -1423,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>26</v>
@@ -1435,31 +1441,29 @@
         <v>62</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>172</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O2" s="6"/>
       <c r="P2" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="112" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="304" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#yiparrartu</v>
@@ -1468,13 +1472,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>26</v>
@@ -1483,34 +1487,34 @@
         <v>27</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="128" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="272" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#jamut</v>
@@ -1519,13 +1523,13 @@
         <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>26</v>
@@ -1534,34 +1538,34 @@
         <v>27</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>71</v>
+        <v>254</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="112" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#jikirrij</v>
@@ -1570,13 +1574,13 @@
         <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>26</v>
@@ -1585,31 +1589,31 @@
         <v>27</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="80" x14ac:dyDescent="0.2">
@@ -1621,13 +1625,13 @@
         <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>26</v>
@@ -1636,31 +1640,31 @@
         <v>27</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="96" x14ac:dyDescent="0.2">
@@ -1672,13 +1676,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>26</v>
@@ -1687,34 +1691,34 @@
         <v>27</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="160" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="272" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#niinii</v>
@@ -1723,16 +1727,16 @@
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>26</v>
@@ -1741,31 +1745,31 @@
         <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>269</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -1777,13 +1781,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>26</v>
@@ -1792,31 +1796,31 @@
         <v>27</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="64" x14ac:dyDescent="0.2">
@@ -1828,16 +1832,16 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>26</v>
@@ -1846,32 +1850,30 @@
         <v>27</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>180</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Q10" s="6"/>
     </row>
     <row r="11" spans="1:17" ht="128" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="str">
@@ -1882,13 +1884,13 @@
         <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
@@ -1897,31 +1899,31 @@
         <v>27</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="48" x14ac:dyDescent="0.2">
@@ -1933,13 +1935,13 @@
         <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>26</v>
@@ -1948,34 +1950,32 @@
         <v>27</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>164</v>
+        <v>249</v>
+      </c>
+      <c r="O12" s="6"/>
+      <c r="P12" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="112" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="128" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#kurtakurtaka</v>
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>26</v>
@@ -1999,34 +1999,34 @@
         <v>27</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>268</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="64" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#kurrarntal</v>
@@ -2035,13 +2035,13 @@
         <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>26</v>
@@ -2050,31 +2050,31 @@
         <v>27</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>265</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="64" x14ac:dyDescent="0.2">
@@ -2086,13 +2086,13 @@
         <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
@@ -2101,34 +2101,34 @@
         <v>27</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="112" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#karrangkarrang</v>
@@ -2137,13 +2137,13 @@
         <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>26</v>
@@ -2152,31 +2152,31 @@
         <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="O16" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="48" x14ac:dyDescent="0.2">
@@ -2188,13 +2188,13 @@
         <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>26</v>
@@ -2203,31 +2203,31 @@
         <v>27</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -2239,13 +2239,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>26</v>
@@ -2254,32 +2254,28 @@
         <v>27</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O18" s="6"/>
       <c r="P18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="str">
@@ -2290,13 +2286,13 @@
         <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>26</v>
@@ -2305,31 +2301,31 @@
         <v>27</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="64" x14ac:dyDescent="0.2">
@@ -2341,13 +2337,13 @@
         <v>25</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>26</v>
@@ -2356,32 +2352,30 @@
         <v>27</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Q20" s="6"/>
     </row>
     <row r="21" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="str">
@@ -2392,16 +2386,16 @@
         <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -2410,31 +2404,31 @@
         <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2466,222 +2460,222 @@
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2692,205 +2686,205 @@
         <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2901,161 +2895,161 @@
         <v>31</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B51" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -3066,216 +3060,216 @@
         <v>31</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B57" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B59" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B67" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B68" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B73" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B74" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3306,13 +3300,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3460,16 +3454,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
